--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260930.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260930.xlsx
@@ -843,17 +843,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>1,167,617</t>
+          <t>536,404</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>536,404</t>
+          <t>1,167,617</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>162,000</t>
+          <t>5,350,296</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>5,350,296</t>
+          <t>162,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>12,694,134</t>
+          <t>1,366,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1,366,000</t>
+          <t>12,694,134</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>796,897</t>
+          <t>433,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,974,587</t>
+          <t>796,897</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>433,000</t>
+          <t>1,974,587</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,291,384</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>7,067,249</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>7,067,249</t>
+          <t>1,291,384</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>4,015,578</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>4,015,578</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202610WVHFV6F</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>765,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>202610WVHFV6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>2,159,107</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>765,000</t>
+          <t>2,159,107</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>224,000</t>
+          <t>1,168,076</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>1,168,076</t>
+          <t>224,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>315,000</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>286,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>286,000</t>
+          <t>315,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>晶豪科</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>409,000</t>
+          <t>1,733,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,733,000</t>
+          <t>1,113,121</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>晶豪科</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>1,113,121</t>
+          <t>409,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>326,000</t>
+          <t>168,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>168,000</t>
+          <t>63,538</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>63,538</t>
+          <t>113,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>113,000</t>
+          <t>326,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>670,000</t>
+          <t>154,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>154,000</t>
+          <t>670,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
